--- a/railway-backend/afl_fixtures_2026.xlsx
+++ b/railway-backend/afl_fixtures_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FlutterProjects\my_app\railway-backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1633542-0948-4D99-9E01-AD26392F51B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{206B2049-A4CA-4801-B138-41D4BDE7D5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FAFE0CD9-9BC2-49F0-B524-DEB3075BE8E7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FAFE0CD9-9BC2-49F0-B524-DEB3075BE8E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="718">
   <si>
     <t>ROUND</t>
   </si>
@@ -2099,6 +2099,12 @@
     <t>SF</t>
   </si>
   <si>
+    <t>PF</t>
+  </si>
+  <si>
+    <t>GF</t>
+  </si>
+  <si>
     <t>Thursday September 3</t>
   </si>
   <si>
@@ -2166,6 +2172,27 @@
   </si>
   <si>
     <t>CD_M20260142702</t>
+  </si>
+  <si>
+    <t>Friday September 18</t>
+  </si>
+  <si>
+    <t>Saturday September 19</t>
+  </si>
+  <si>
+    <t>5:15pm</t>
+  </si>
+  <si>
+    <t>CD_M20260142802</t>
+  </si>
+  <si>
+    <t>CD_M20260142801</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/9027</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/9026</t>
   </si>
 </sst>
 </file>
@@ -2564,7 +2591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB6B02A0-21B2-418E-97BD-054996A22EC7}">
-  <dimension ref="A1:I225"/>
+  <dimension ref="A1:I228"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
@@ -8874,7 +8901,7 @@
         <v>2026</v>
       </c>
       <c r="B218" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C218" t="s">
         <v>676</v>
@@ -8903,7 +8930,7 @@
         <v>2026</v>
       </c>
       <c r="B219" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C219" t="s">
         <v>680</v>
@@ -8935,25 +8962,25 @@
         <v>684</v>
       </c>
       <c r="C220" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D220" t="s">
         <v>88</v>
       </c>
       <c r="E220" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="F220" t="s">
         <v>304</v>
       </c>
       <c r="G220" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="H220" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="I220" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
@@ -8964,7 +8991,7 @@
         <v>684</v>
       </c>
       <c r="C221" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D221" t="s">
         <v>52</v>
@@ -8979,10 +9006,10 @@
         <v>677</v>
       </c>
       <c r="H221" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="I221" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
@@ -8993,25 +9020,25 @@
         <v>684</v>
       </c>
       <c r="C222" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D222" t="s">
         <v>9</v>
       </c>
       <c r="E222" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="F222" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="G222" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H222" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I222" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
@@ -9022,7 +9049,7 @@
         <v>684</v>
       </c>
       <c r="C223" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D223" t="s">
         <v>80</v>
@@ -9037,10 +9064,10 @@
         <v>681</v>
       </c>
       <c r="H223" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="I223" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
@@ -9051,7 +9078,7 @@
         <v>685</v>
       </c>
       <c r="C224" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D224" t="s">
         <v>88</v>
@@ -9063,13 +9090,13 @@
         <v>304</v>
       </c>
       <c r="G224" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="H224" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="I224" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
@@ -9080,10 +9107,10 @@
         <v>685</v>
       </c>
       <c r="C225" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D225" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E225" t="s">
         <v>80</v>
@@ -9095,10 +9122,76 @@
         <v>681</v>
       </c>
       <c r="H225" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="I225" t="s">
-        <v>708</v>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>2026</v>
+      </c>
+      <c r="B226" t="s">
+        <v>686</v>
+      </c>
+      <c r="C226" t="s">
+        <v>711</v>
+      </c>
+      <c r="D226" t="s">
+        <v>9</v>
+      </c>
+      <c r="E226" t="s">
+        <v>88</v>
+      </c>
+      <c r="F226" t="s">
+        <v>696</v>
+      </c>
+      <c r="G226" t="s">
+        <v>677</v>
+      </c>
+      <c r="H226" t="s">
+        <v>717</v>
+      </c>
+      <c r="I226" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>2026</v>
+      </c>
+      <c r="B227" t="s">
+        <v>686</v>
+      </c>
+      <c r="C227" t="s">
+        <v>712</v>
+      </c>
+      <c r="D227" t="s">
+        <v>691</v>
+      </c>
+      <c r="E227" t="s">
+        <v>695</v>
+      </c>
+      <c r="F227" t="s">
+        <v>299</v>
+      </c>
+      <c r="G227" t="s">
+        <v>713</v>
+      </c>
+      <c r="H227" t="s">
+        <v>716</v>
+      </c>
+      <c r="I227" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>2027</v>
+      </c>
+      <c r="B228" t="s">
+        <v>687</v>
       </c>
     </row>
   </sheetData>

--- a/railway-backend/afl_fixtures_2026.xlsx
+++ b/railway-backend/afl_fixtures_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FlutterProjects\my_app\railway-backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{206B2049-A4CA-4801-B138-41D4BDE7D5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E7C9DE-9C23-4ECE-B332-E4BBBD84CEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FAFE0CD9-9BC2-49F0-B524-DEB3075BE8E7}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FAFE0CD9-9BC2-49F0-B524-DEB3075BE8E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="722">
   <si>
     <t>ROUND</t>
   </si>
@@ -2193,6 +2193,18 @@
   </si>
   <si>
     <t>https://www.afl.com.au/afl/matches/9026</t>
+  </si>
+  <si>
+    <t>Saturday September 26</t>
+  </si>
+  <si>
+    <t>2.30pm</t>
+  </si>
+  <si>
+    <t>https://www.afl.com.au/afl/matches/9028</t>
+  </si>
+  <si>
+    <t>CD_M20260142901</t>
   </si>
 </sst>
 </file>
@@ -9188,10 +9200,31 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B228" t="s">
         <v>687</v>
+      </c>
+      <c r="C228" t="s">
+        <v>718</v>
+      </c>
+      <c r="D228" t="s">
+        <v>88</v>
+      </c>
+      <c r="E228" t="s">
+        <v>695</v>
+      </c>
+      <c r="F228" t="s">
+        <v>299</v>
+      </c>
+      <c r="G228" t="s">
+        <v>719</v>
+      </c>
+      <c r="H228" t="s">
+        <v>720</v>
+      </c>
+      <c r="I228" t="s">
+        <v>721</v>
       </c>
     </row>
   </sheetData>
